--- a/output_data/Grid_Optimization_Results.xlsx
+++ b/output_data/Grid_Optimization_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52764.94017733401</v>
+        <v>54590.91248360416</v>
       </c>
       <c r="C2" t="n">
-        <v>-1260670.314489931</v>
+        <v>-1250471.786129119</v>
       </c>
       <c r="D2" t="n">
-        <v>1783.531378688764</v>
+        <v>1770.003088551764</v>
       </c>
       <c r="E2" t="n">
-        <v>2106.983739687774</v>
+        <v>2081.035203207276</v>
       </c>
       <c r="F2" t="n">
-        <v>1858.852923415626</v>
+        <v>1839.425264193573</v>
       </c>
       <c r="G2" t="n">
-        <v>2104.367034301711</v>
+        <v>2081.013886597711</v>
       </c>
       <c r="H2" t="n">
-        <v>94.34214682355798</v>
+        <v>102.9525166072761</v>
       </c>
       <c r="I2" t="n">
-        <v>393.0153728923834</v>
+        <v>287.1776203071625</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-55287.65793090081</v>
+        <v>-37689.14902832685</v>
       </c>
       <c r="C3" t="n">
-        <v>-1913753.921874943</v>
+        <v>-1911019.520589183</v>
       </c>
       <c r="D3" t="n">
-        <v>1962.426472778364</v>
+        <v>2005.088943423849</v>
       </c>
       <c r="E3" t="n">
-        <v>2728.069816272759</v>
+        <v>2656.327355468585</v>
       </c>
       <c r="F3" t="n">
-        <v>1770.064700538074</v>
+        <v>1770.008255787954</v>
       </c>
       <c r="G3" t="n">
-        <v>2104.353155881144</v>
+        <v>2081.203451100079</v>
       </c>
       <c r="H3" t="n">
-        <v>95.26253999359395</v>
+        <v>102.5123125935481</v>
       </c>
       <c r="I3" t="n">
-        <v>107.8791895369515</v>
+        <v>107.3803014283374</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-55320.63353940612</v>
+        <v>84631.83699445287</v>
       </c>
       <c r="C4" t="n">
-        <v>-1913649.017784521</v>
+        <v>-1482080.05227496</v>
       </c>
       <c r="D4" t="n">
-        <v>1962.377406109479</v>
+        <v>1775.099020729065</v>
       </c>
       <c r="E4" t="n">
-        <v>2727.979825174754</v>
+        <v>2334.575972698455</v>
       </c>
       <c r="F4" t="n">
-        <v>1770.008345541769</v>
+        <v>1914.618860179588</v>
       </c>
       <c r="G4" t="n">
-        <v>2104.414179287996</v>
+        <v>2081.75436549542</v>
       </c>
       <c r="H4" t="n">
-        <v>102.4974506865347</v>
+        <v>125.3983522241774</v>
       </c>
       <c r="I4" t="n">
-        <v>100.2179153934797</v>
+        <v>153.7601155505577</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8355.175413845573</v>
+        <v>-37659.01421718253</v>
       </c>
       <c r="C5" t="n">
-        <v>-1249561.83601666</v>
+        <v>-1911756.215558813</v>
       </c>
       <c r="D5" t="n">
-        <v>1770.001788193461</v>
+        <v>2006.069370211739</v>
       </c>
       <c r="E5" t="n">
-        <v>2103.000739415814</v>
+        <v>2656.327355468585</v>
       </c>
       <c r="F5" t="n">
-        <v>1781.567769519467</v>
+        <v>1770.016509606354</v>
       </c>
       <c r="G5" t="n">
-        <v>2103.01631814021</v>
+        <v>2081.207227974789</v>
       </c>
       <c r="H5" t="n">
-        <v>97.20604839254315</v>
+        <v>104.5712464633992</v>
       </c>
       <c r="I5" t="n">
-        <v>113.4291252952041</v>
+        <v>107.658651438933</v>
       </c>
     </row>
     <row r="6">
@@ -606,28 +606,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26600.55144407833</v>
+        <v>36715.47008610889</v>
       </c>
       <c r="C6" t="n">
-        <v>-1305801.355214697</v>
+        <v>-1447601.59130361</v>
       </c>
       <c r="D6" t="n">
-        <v>1790.125324498429</v>
+        <v>1878.638748125504</v>
       </c>
       <c r="E6" t="n">
-        <v>2143.028979150441</v>
+        <v>2191.142842809537</v>
       </c>
       <c r="F6" t="n">
-        <v>1838.671074619496</v>
+        <v>1845.057347631956</v>
       </c>
       <c r="G6" t="n">
-        <v>2104.216204648587</v>
+        <v>2081.428039496444</v>
       </c>
       <c r="H6" t="n">
-        <v>102.3367420258623</v>
+        <v>101.0472354758767</v>
       </c>
       <c r="I6" t="n">
-        <v>108.3543741382289</v>
+        <v>126.6117985537857</v>
       </c>
     </row>
     <row r="7">
@@ -637,28 +637,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34753.92091272539</v>
+        <v>72176.50674757315</v>
       </c>
       <c r="C7" t="n">
-        <v>-1287661.798245452</v>
+        <v>-1567593.035196026</v>
       </c>
       <c r="D7" t="n">
-        <v>1775.751661360702</v>
+        <v>2116.443392266772</v>
       </c>
       <c r="E7" t="n">
-        <v>2141.398825504447</v>
+        <v>2098.002843073334</v>
       </c>
       <c r="F7" t="n">
-        <v>1846.003973419843</v>
+        <v>1905.075734392841</v>
       </c>
       <c r="G7" t="n">
-        <v>2104.207635936095</v>
+        <v>2081.203355526613</v>
       </c>
       <c r="H7" t="n">
-        <v>97.90311601693057</v>
+        <v>107.5304198922858</v>
       </c>
       <c r="I7" t="n">
-        <v>102.6489918839438</v>
+        <v>131.011675092824</v>
       </c>
     </row>
     <row r="8">
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-497.9003639901057</v>
+        <v>64618.00131437881</v>
       </c>
       <c r="C8" t="n">
-        <v>-1782766.068596523</v>
+        <v>-1252786.580899253</v>
       </c>
       <c r="D8" t="n">
-        <v>1973.066025981699</v>
+        <v>1770.631639147685</v>
       </c>
       <c r="E8" t="n">
-        <v>2546.912915432899</v>
+        <v>2084.368889245448</v>
       </c>
       <c r="F8" t="n">
-        <v>1838.946620808924</v>
+        <v>1857.411293476401</v>
       </c>
       <c r="G8" t="n">
-        <v>2103.038295823162</v>
+        <v>2081.434759432201</v>
       </c>
       <c r="H8" t="n">
-        <v>95.22604564855068</v>
+        <v>108.9265693306009</v>
       </c>
       <c r="I8" t="n">
-        <v>156.7807470244786</v>
+        <v>102.3751098019345</v>
       </c>
     </row>
     <row r="9">
@@ -699,28 +699,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-52070.28544496233</v>
+        <v>30449.86110013304</v>
       </c>
       <c r="C9" t="n">
-        <v>-1835347.14141486</v>
+        <v>-1402643.437161177</v>
       </c>
       <c r="D9" t="n">
-        <v>2428.326967249547</v>
+        <v>1934.161539438257</v>
       </c>
       <c r="E9" t="n">
-        <v>2158.689001996935</v>
+        <v>2083.062581404575</v>
       </c>
       <c r="F9" t="n">
-        <v>1770.696454129759</v>
+        <v>1831.868929221982</v>
       </c>
       <c r="G9" t="n">
-        <v>2103.054177487224</v>
+        <v>2081.270000490099</v>
       </c>
       <c r="H9" t="n">
-        <v>99.91852095470838</v>
+        <v>105.4234583375693</v>
       </c>
       <c r="I9" t="n">
-        <v>108.5848653219252</v>
+        <v>101.2568942758483</v>
       </c>
     </row>
     <row r="10">
@@ -730,28 +730,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-53895.57993762335</v>
+        <v>-35472.85924750427</v>
       </c>
       <c r="C10" t="n">
-        <v>-1863604.66808374</v>
+        <v>-1902128.382280094</v>
       </c>
       <c r="D10" t="n">
-        <v>1962.421133603824</v>
+        <v>1956.608806406684</v>
       </c>
       <c r="E10" t="n">
-        <v>2661.454219547797</v>
+        <v>2693.36185836626</v>
       </c>
       <c r="F10" t="n">
-        <v>1770.121826383188</v>
+        <v>1770.489586546531</v>
       </c>
       <c r="G10" t="n">
-        <v>2103.915547696184</v>
+        <v>2089.023687369966</v>
       </c>
       <c r="H10" t="n">
-        <v>97.54317562986944</v>
+        <v>108.8349889077549</v>
       </c>
       <c r="I10" t="n">
-        <v>108.0946456179657</v>
+        <v>123.8654825791614</v>
       </c>
     </row>
     <row r="11">
@@ -761,28 +761,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-35857.60391743435</v>
+        <v>-31145.70925396634</v>
       </c>
       <c r="C11" t="n">
-        <v>-1488349.260147285</v>
+        <v>-1814348.288104942</v>
       </c>
       <c r="D11" t="n">
-        <v>1986.840929953099</v>
+        <v>1914.658496512258</v>
       </c>
       <c r="E11" t="n">
-        <v>2139.89985871583</v>
+        <v>2619.141368486241</v>
       </c>
       <c r="F11" t="n">
-        <v>1780.173665044352</v>
+        <v>1771.082468885047</v>
       </c>
       <c r="G11" t="n">
-        <v>2103.91035022683</v>
+        <v>2097.387128838186</v>
       </c>
       <c r="H11" t="n">
-        <v>99.95958906474166</v>
+        <v>105.6368023921698</v>
       </c>
       <c r="I11" t="n">
-        <v>111.5380454406894</v>
+        <v>136.6946848419097</v>
       </c>
     </row>
     <row r="12">
@@ -792,28 +792,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3672.461017196067</v>
+        <v>-5302.477842391934</v>
       </c>
       <c r="C12" t="n">
-        <v>-1910231.535172125</v>
+        <v>-1834255.147862811</v>
       </c>
       <c r="D12" t="n">
-        <v>2462.265248613631</v>
+        <v>2407.941118005044</v>
       </c>
       <c r="E12" t="n">
-        <v>2227.78578645489</v>
+        <v>2154.115244003367</v>
       </c>
       <c r="F12" t="n">
-        <v>1838.667919971536</v>
+        <v>1809.535538339525</v>
       </c>
       <c r="G12" t="n">
-        <v>2104.699922500767</v>
+        <v>2081.019786209644</v>
       </c>
       <c r="H12" t="n">
-        <v>99.47146799116915</v>
+        <v>119.0802256818233</v>
       </c>
       <c r="I12" t="n">
-        <v>124.3001091364015</v>
+        <v>129.5888679361906</v>
       </c>
     </row>
     <row r="13">
@@ -823,28 +823,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-51461.69258945575</v>
+        <v>2808.920963238459</v>
       </c>
       <c r="C13" t="n">
-        <v>-1819926.297886304</v>
+        <v>-1264482.824539011</v>
       </c>
       <c r="D13" t="n">
-        <v>2423.921205415726</v>
+        <v>1773.810371973025</v>
       </c>
       <c r="E13" t="n">
-        <v>2142.628153851582</v>
+        <v>2091.487077989502</v>
       </c>
       <c r="F13" t="n">
-        <v>1771.076220692603</v>
+        <v>1770.980081684322</v>
       </c>
       <c r="G13" t="n">
-        <v>2103.060101342527</v>
+        <v>2081.036403404537</v>
       </c>
       <c r="H13" t="n">
-        <v>95.29970969248271</v>
+        <v>115.6153462329939</v>
       </c>
       <c r="I13" t="n">
-        <v>108.3543741382289</v>
+        <v>222.439293447543</v>
       </c>
     </row>
     <row r="14">
@@ -854,28 +854,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-46427.71423996193</v>
+        <v>81063.03829449555</v>
       </c>
       <c r="C14" t="n">
-        <v>-1875679.950855702</v>
+        <v>-1523356.022272883</v>
       </c>
       <c r="D14" t="n">
-        <v>2533.45995737291</v>
+        <v>1774.3289573396</v>
       </c>
       <c r="E14" t="n">
-        <v>2107.730956054163</v>
+        <v>2379.523484620863</v>
       </c>
       <c r="F14" t="n">
-        <v>1779.674557723061</v>
+        <v>1916.925339863042</v>
       </c>
       <c r="G14" t="n">
-        <v>2103.071529039782</v>
+        <v>2081.741500352002</v>
       </c>
       <c r="H14" t="n">
-        <v>100.0376648896126</v>
+        <v>126.536154850077</v>
       </c>
       <c r="I14" t="n">
-        <v>108.4237186613745</v>
+        <v>114.3914053288611</v>
       </c>
     </row>
     <row r="15">
@@ -885,28 +885,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-42432.29758139746</v>
+        <v>46196.5341366739</v>
       </c>
       <c r="C15" t="n">
-        <v>-1474540.426641684</v>
+        <v>-1437547.818678087</v>
       </c>
       <c r="D15" t="n">
-        <v>1960.391491118183</v>
+        <v>1775.725142625957</v>
       </c>
       <c r="E15" t="n">
-        <v>2149.564444180117</v>
+        <v>2282.219401992822</v>
       </c>
       <c r="F15" t="n">
-        <v>1770.000839552447</v>
+        <v>1854.89536663513</v>
       </c>
       <c r="G15" t="n">
-        <v>2104.054702635934</v>
+        <v>2081.75436549542</v>
       </c>
       <c r="H15" t="n">
-        <v>95.32828739453616</v>
+        <v>125.3983522241774</v>
       </c>
       <c r="I15" t="n">
-        <v>107.8833269753758</v>
+        <v>199.238118262282</v>
       </c>
     </row>
     <row r="16">
@@ -916,28 +916,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-27635.42763623456</v>
+        <v>-16932.72587826382</v>
       </c>
       <c r="C16" t="n">
-        <v>-1726478.998660363</v>
+        <v>-1534153.511797696</v>
       </c>
       <c r="D16" t="n">
-        <v>2336.081445684262</v>
+        <v>1770.039813060577</v>
       </c>
       <c r="E16" t="n">
-        <v>2107.465240081438</v>
+        <v>2391.091846218555</v>
       </c>
       <c r="F16" t="n">
-        <v>1795.258253673003</v>
+        <v>1781.191541997141</v>
       </c>
       <c r="G16" t="n">
-        <v>2103.107681748633</v>
+        <v>2081.04338008953</v>
       </c>
       <c r="H16" t="n">
-        <v>98.21145126034406</v>
+        <v>103.1111465909227</v>
       </c>
       <c r="I16" t="n">
-        <v>311.7996615375134</v>
+        <v>253.4189870119677</v>
       </c>
     </row>
     <row r="17">
@@ -947,28 +947,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-13265.45454418706</v>
+        <v>-36474.55789615726</v>
       </c>
       <c r="C17" t="n">
-        <v>-1710523.513666461</v>
+        <v>-1886205.102543321</v>
       </c>
       <c r="D17" t="n">
-        <v>2270.878488185627</v>
+        <v>1997.731510016918</v>
       </c>
       <c r="E17" t="n">
-        <v>2152.440094272631</v>
+        <v>2630.747630850421</v>
       </c>
       <c r="F17" t="n">
-        <v>1813.601424738795</v>
+        <v>1770.025442340707</v>
       </c>
       <c r="G17" t="n">
-        <v>2105.530372394847</v>
+        <v>2081.732448665513</v>
       </c>
       <c r="H17" t="n">
-        <v>104.7612311979386</v>
+        <v>106.7331235801283</v>
       </c>
       <c r="I17" t="n">
-        <v>315.1332495426022</v>
+        <v>128.2220208632673</v>
       </c>
     </row>
     <row r="18">
@@ -978,28 +978,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-49923.03906602692</v>
+        <v>9882.139592497144</v>
       </c>
       <c r="C18" t="n">
-        <v>-1792494.493679129</v>
+        <v>-1272076.651655533</v>
       </c>
       <c r="D18" t="n">
-        <v>2421.50990376878</v>
+        <v>1770.009401490086</v>
       </c>
       <c r="E18" t="n">
-        <v>2108.664632980717</v>
+        <v>2105.138362840213</v>
       </c>
       <c r="F18" t="n">
-        <v>1771.076220692603</v>
+        <v>1784.792947151513</v>
       </c>
       <c r="G18" t="n">
-        <v>2104.200447059387</v>
+        <v>2081.03424249566</v>
       </c>
       <c r="H18" t="n">
-        <v>128.5250365202877</v>
+        <v>93.58478486678243</v>
       </c>
       <c r="I18" t="n">
-        <v>108.3543741382289</v>
+        <v>100.9239192716115</v>
       </c>
     </row>
     <row r="19">
@@ -1009,28 +1009,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-52782.32721834583</v>
+        <v>17575.4023392885</v>
       </c>
       <c r="C19" t="n">
-        <v>-1886432.862065025</v>
+        <v>-1843254.409764558</v>
       </c>
       <c r="D19" t="n">
-        <v>2478.705769145735</v>
+        <v>1955.369771944423</v>
       </c>
       <c r="E19" t="n">
-        <v>2176.331397730668</v>
+        <v>2619.632558998585</v>
       </c>
       <c r="F19" t="n">
-        <v>1771.48979204685</v>
+        <v>1842.235762379752</v>
       </c>
       <c r="G19" t="n">
-        <v>2104.246483209567</v>
+        <v>2081.016885382162</v>
       </c>
       <c r="H19" t="n">
-        <v>95.29970969248271</v>
+        <v>127.8724576088553</v>
       </c>
       <c r="I19" t="n">
-        <v>103.9718185092763</v>
+        <v>111.2697984871154</v>
       </c>
     </row>
     <row r="20">
@@ -1040,28 +1040,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-46687.27219941607</v>
+        <v>-22637.15869275155</v>
       </c>
       <c r="C20" t="n">
-        <v>-1643341.60269751</v>
+        <v>-1602910.981103168</v>
       </c>
       <c r="D20" t="n">
-        <v>2037.322769667729</v>
+        <v>1914.658496512258</v>
       </c>
       <c r="E20" t="n">
-        <v>2294.171864420567</v>
+        <v>2338.341122437847</v>
       </c>
       <c r="F20" t="n">
-        <v>1771.444945493829</v>
+        <v>1771.082468885047</v>
       </c>
       <c r="G20" t="n">
-        <v>2103.217966882171</v>
+        <v>2097.387128838186</v>
       </c>
       <c r="H20" t="n">
-        <v>99.3751838790066</v>
+        <v>105.7106076939836</v>
       </c>
       <c r="I20" t="n">
-        <v>116.8792409186017</v>
+        <v>289.4994354409251</v>
       </c>
     </row>
     <row r="21">
@@ -1071,28 +1071,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-6625.142140727025</v>
+        <v>41506.67172864405</v>
       </c>
       <c r="C21" t="n">
-        <v>-1258208.428282379</v>
+        <v>-1373194.104105351</v>
       </c>
       <c r="D21" t="n">
-        <v>1775.015655745782</v>
+        <v>1848.628186343077</v>
       </c>
       <c r="E21" t="n">
-        <v>2109.144594083681</v>
+        <v>2136.646596443357</v>
       </c>
       <c r="F21" t="n">
-        <v>1784.450897834886</v>
+        <v>1842.610488904649</v>
       </c>
       <c r="G21" t="n">
-        <v>2103.014133492477</v>
+        <v>2081.022068080504</v>
       </c>
       <c r="H21" t="n">
-        <v>97.23032575336065</v>
+        <v>102.5008617633834</v>
       </c>
       <c r="I21" t="n">
-        <v>113.3335298178321</v>
+        <v>125.4732637393464</v>
       </c>
     </row>
     <row r="22">
@@ -1102,28 +1102,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-25978.5416985834</v>
+        <v>-18463.36686337506</v>
       </c>
       <c r="C22" t="n">
-        <v>-1590756.226205498</v>
+        <v>-1458458.265935071</v>
       </c>
       <c r="D22" t="n">
-        <v>2149.008807105173</v>
+        <v>1884.073615301734</v>
       </c>
       <c r="E22" t="n">
-        <v>2114.109771404209</v>
+        <v>2195.137602818731</v>
       </c>
       <c r="F22" t="n">
-        <v>1797.151283765605</v>
+        <v>1770.980081684322</v>
       </c>
       <c r="G22" t="n">
-        <v>2103.0643843105</v>
+        <v>2081.036403404537</v>
       </c>
       <c r="H22" t="n">
-        <v>129.1086698915789</v>
+        <v>105.6806005671124</v>
       </c>
       <c r="I22" t="n">
-        <v>101.1851657981448</v>
+        <v>116.5578059068876</v>
       </c>
     </row>
     <row r="23">
@@ -1133,28 +1133,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-31676.58220811747</v>
+        <v>74376.72674609441</v>
       </c>
       <c r="C23" t="n">
-        <v>-1408994.261885603</v>
+        <v>-1284304.527534404</v>
       </c>
       <c r="D23" t="n">
-        <v>1934.553503568262</v>
+        <v>1770.170099040127</v>
       </c>
       <c r="E23" t="n">
-        <v>2104.229698889871</v>
+        <v>2120.307399460822</v>
       </c>
       <c r="F23" t="n">
-        <v>1775.452199045443</v>
+        <v>1874.873219490557</v>
       </c>
       <c r="G23" t="n">
-        <v>2103.135212807635</v>
+        <v>2081.714314436108</v>
       </c>
       <c r="H23" t="n">
-        <v>97.70773177250832</v>
+        <v>109.7814020658818</v>
       </c>
       <c r="I23" t="n">
-        <v>112.1297376158123</v>
+        <v>107.3945071403872</v>
       </c>
     </row>
     <row r="24">
@@ -1164,28 +1164,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-46261.86765687214</v>
+        <v>25114.53123787651</v>
       </c>
       <c r="C24" t="n">
-        <v>-1631717.710178371</v>
+        <v>-1662278.390020732</v>
       </c>
       <c r="D24" t="n">
-        <v>2083.365097747004</v>
+        <v>2167.98729824838</v>
       </c>
       <c r="E24" t="n">
-        <v>2232.74710706625</v>
+        <v>2167.166862367499</v>
       </c>
       <c r="F24" t="n">
-        <v>1770.011161532615</v>
+        <v>1845.865885478821</v>
       </c>
       <c r="G24" t="n">
-        <v>2104.362728382394</v>
+        <v>2081.045242047006</v>
       </c>
       <c r="H24" t="n">
-        <v>132.8718203094823</v>
+        <v>111.0446951795611</v>
       </c>
       <c r="I24" t="n">
-        <v>133.4179606053357</v>
+        <v>104.3967196562919</v>
       </c>
     </row>
     <row r="25">
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>47558.31198241515</v>
+        <v>-35466.50863610255</v>
       </c>
       <c r="C25" t="n">
-        <v>-1264123.56875621</v>
+        <v>-1830037.220546103</v>
       </c>
       <c r="D25" t="n">
-        <v>1785.876596809</v>
+        <v>2005.088943423849</v>
       </c>
       <c r="E25" t="n">
-        <v>2109.129828631882</v>
+        <v>2548.778924451474</v>
       </c>
       <c r="F25" t="n">
-        <v>1859.015379617762</v>
+        <v>1770.004347551575</v>
       </c>
       <c r="G25" t="n">
-        <v>2103.18720198523</v>
+        <v>2081.216207510498</v>
       </c>
       <c r="H25" t="n">
-        <v>99.3751838790066</v>
+        <v>102.4851729590631</v>
       </c>
       <c r="I25" t="n">
-        <v>103.5111591102922</v>
+        <v>107.3803014283374</v>
       </c>
     </row>
     <row r="26">
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43477.12076112954</v>
+        <v>17156.77979886299</v>
       </c>
       <c r="C26" t="n">
-        <v>-1295407.356966567</v>
+        <v>-1631356.363052523</v>
       </c>
       <c r="D26" t="n">
-        <v>1813.670767946848</v>
+        <v>1772.681200728404</v>
       </c>
       <c r="E26" t="n">
-        <v>2111.20986419564</v>
+        <v>2520.25261735711</v>
       </c>
       <c r="F26" t="n">
-        <v>1859.015379617762</v>
+        <v>1834.494761202528</v>
       </c>
       <c r="G26" t="n">
-        <v>2104.261081489547</v>
+        <v>2081.104723623764</v>
       </c>
       <c r="H26" t="n">
-        <v>98.13508838836947</v>
+        <v>111.6906702213406</v>
       </c>
       <c r="I26" t="n">
-        <v>123.582998545688</v>
+        <v>111.3107595148616</v>
       </c>
     </row>
     <row r="27">
@@ -1257,28 +1257,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-32449.41717309877</v>
+        <v>-28221.01022536028</v>
       </c>
       <c r="C27" t="n">
-        <v>-1539594.605624637</v>
+        <v>-1680535.751710963</v>
       </c>
       <c r="D27" t="n">
-        <v>1998.112497928568</v>
+        <v>2264.207995440653</v>
       </c>
       <c r="E27" t="n">
-        <v>2196.079079681953</v>
+        <v>2091.541099778217</v>
       </c>
       <c r="F27" t="n">
-        <v>1782.161051643769</v>
+        <v>1770.977331468597</v>
       </c>
       <c r="G27" t="n">
-        <v>2103.074101012696</v>
+        <v>2081.168484184072</v>
       </c>
       <c r="H27" t="n">
-        <v>101.8342813546464</v>
+        <v>111.3449587587219</v>
       </c>
       <c r="I27" t="n">
-        <v>318.7181915623534</v>
+        <v>213.430214344542</v>
       </c>
     </row>
     <row r="28">
@@ -1288,28 +1288,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-28792.66071303142</v>
+        <v>49514.07663473347</v>
       </c>
       <c r="C28" t="n">
-        <v>-1339980.158035571</v>
+        <v>-1325935.79861155</v>
       </c>
       <c r="D28" t="n">
-        <v>1788.116345736658</v>
+        <v>1771.50446988254</v>
       </c>
       <c r="E28" t="n">
-        <v>2174.921388036477</v>
+        <v>2161.461677569777</v>
       </c>
       <c r="F28" t="n">
-        <v>1770.091054186865</v>
+        <v>1847.152346025718</v>
       </c>
       <c r="G28" t="n">
-        <v>2103.01631814021</v>
+        <v>2081.04519391525</v>
       </c>
       <c r="H28" t="n">
-        <v>91.29401569859215</v>
+        <v>134.3603589226105</v>
       </c>
       <c r="I28" t="n">
-        <v>113.4291252952041</v>
+        <v>102.9777412377591</v>
       </c>
     </row>
     <row r="29">
@@ -1319,28 +1319,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-47446.94588946365</v>
+        <v>-14947.39243176254</v>
       </c>
       <c r="C29" t="n">
-        <v>-1689468.975840991</v>
+        <v>-1412625.558631771</v>
       </c>
       <c r="D29" t="n">
-        <v>2284.484783767595</v>
+        <v>1943.439642403804</v>
       </c>
       <c r="E29" t="n">
-        <v>2108.664632980717</v>
+        <v>2082.261043690888</v>
       </c>
       <c r="F29" t="n">
-        <v>1771.067435782926</v>
+        <v>1770.734618679671</v>
       </c>
       <c r="G29" t="n">
-        <v>2104.200447059387</v>
+        <v>2081.364819258835</v>
       </c>
       <c r="H29" t="n">
-        <v>127.2780441835696</v>
+        <v>119.1028024076633</v>
       </c>
       <c r="I29" t="n">
-        <v>101.9628263670812</v>
+        <v>100.6570559049968</v>
       </c>
     </row>
     <row r="30">
@@ -1350,28 +1350,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-42042.81800961355</v>
+        <v>-35022.41552790022</v>
       </c>
       <c r="C30" t="n">
-        <v>-1735107.707125805</v>
+        <v>-1807633.960073248</v>
       </c>
       <c r="D30" t="n">
-        <v>2346.618240929961</v>
+        <v>1868.564588809503</v>
       </c>
       <c r="E30" t="n">
-        <v>2107.760727908237</v>
+        <v>2655.378538347897</v>
       </c>
       <c r="F30" t="n">
-        <v>1780.173665044352</v>
+        <v>1770.025481758198</v>
       </c>
       <c r="G30" t="n">
-        <v>2105.454517181174</v>
+        <v>2081.739718519888</v>
       </c>
       <c r="H30" t="n">
-        <v>99.97482989613157</v>
+        <v>104.8840019603399</v>
       </c>
       <c r="I30" t="n">
-        <v>111.5380454406894</v>
+        <v>101.3902575821652</v>
       </c>
     </row>
     <row r="31">
@@ -1381,28 +1381,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-34797.37259441381</v>
+        <v>-29856.16057212045</v>
       </c>
       <c r="C31" t="n">
-        <v>-1512821.327477489</v>
+        <v>-1672693.227540672</v>
       </c>
       <c r="D31" t="n">
-        <v>1887.796705140971</v>
+        <v>2264.207995440653</v>
       </c>
       <c r="E31" t="n">
-        <v>2270.728347279755</v>
+        <v>2081.109806242288</v>
       </c>
       <c r="F31" t="n">
-        <v>1783.00361988802</v>
+        <v>1770.662076710149</v>
       </c>
       <c r="G31" t="n">
-        <v>2103.247372730241</v>
+        <v>2081.168484184072</v>
       </c>
       <c r="H31" t="n">
-        <v>106.1287315926706</v>
+        <v>111.3632617704126</v>
       </c>
       <c r="I31" t="n">
-        <v>112.9184139186295</v>
+        <v>121.7985008528401</v>
       </c>
     </row>
     <row r="32">
@@ -1412,28 +1412,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-50792.10255440231</v>
+        <v>16590.94541740883</v>
       </c>
       <c r="C32" t="n">
-        <v>-1803519.212342637</v>
+        <v>-1468015.460124188</v>
       </c>
       <c r="D32" t="n">
-        <v>2436.119567855145</v>
+        <v>1932.768227285749</v>
       </c>
       <c r="E32" t="n">
-        <v>2108.664632980717</v>
+        <v>2160.118895870628</v>
       </c>
       <c r="F32" t="n">
-        <v>1771.232546099468</v>
+        <v>1820.058087585267</v>
       </c>
       <c r="G32" t="n">
-        <v>2103.031473312521</v>
+        <v>2081.554591570587</v>
       </c>
       <c r="H32" t="n">
-        <v>100.2420329399517</v>
+        <v>102.8809222477872</v>
       </c>
       <c r="I32" t="n">
-        <v>108.4015123686044</v>
+        <v>100.7196727953051</v>
       </c>
     </row>
     <row r="33">
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-47922.68736925395</v>
+        <v>14608.17741754372</v>
       </c>
       <c r="C33" t="n">
-        <v>-1842434.844457857</v>
+        <v>-1688474.907253538</v>
       </c>
       <c r="D33" t="n">
-        <v>2478.705769145735</v>
+        <v>2011.16932783774</v>
       </c>
       <c r="E33" t="n">
-        <v>2117.899636822784</v>
+        <v>2357.852111076778</v>
       </c>
       <c r="F33" t="n">
-        <v>1771.48979204685</v>
+        <v>1831.978004482967</v>
       </c>
       <c r="G33" t="n">
-        <v>2104.246483209567</v>
+        <v>2081.269642528914</v>
       </c>
       <c r="H33" t="n">
-        <v>95.29970969248271</v>
+        <v>137.7672246825922</v>
       </c>
       <c r="I33" t="n">
-        <v>310.5566649469059</v>
+        <v>111.2876446557556</v>
       </c>
     </row>
     <row r="34">
@@ -1474,28 +1474,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-33137.02091010567</v>
+        <v>-12665.63365495158</v>
       </c>
       <c r="C34" t="n">
-        <v>-1768724.675452802</v>
+        <v>-1421906.68842821</v>
       </c>
       <c r="D34" t="n">
-        <v>2344.034694220751</v>
+        <v>1953.793790253309</v>
       </c>
       <c r="E34" t="n">
-        <v>2155.528081385331</v>
+        <v>2083.017240439744</v>
       </c>
       <c r="F34" t="n">
-        <v>1793.179467073326</v>
+        <v>1774.538762190334</v>
       </c>
       <c r="G34" t="n">
-        <v>2103.209494501877</v>
+        <v>2081.278621191688</v>
       </c>
       <c r="H34" t="n">
-        <v>121.3497477655236</v>
+        <v>116.105692373568</v>
       </c>
       <c r="I34" t="n">
-        <v>127.1164105790356</v>
+        <v>115.0070289243696</v>
       </c>
     </row>
     <row r="35">
@@ -1505,28 +1505,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-17756.01672083279</v>
+        <v>12416.0420709406</v>
       </c>
       <c r="C35" t="n">
-        <v>-1777188.873806654</v>
+        <v>-1743548.508135494</v>
       </c>
       <c r="D35" t="n">
-        <v>2315.05998183874</v>
+        <v>2075.131577792698</v>
       </c>
       <c r="E35" t="n">
-        <v>2196.570234410563</v>
+        <v>2367.05722098674</v>
       </c>
       <c r="F35" t="n">
-        <v>1810.4482604641</v>
+        <v>1830.878112176465</v>
       </c>
       <c r="G35" t="n">
-        <v>2103.074029714223</v>
+        <v>2081.050084369174</v>
       </c>
       <c r="H35" t="n">
-        <v>100.6889683338215</v>
+        <v>135.4547225244114</v>
       </c>
       <c r="I35" t="n">
-        <v>318.7181915623534</v>
+        <v>117.3156663465249</v>
       </c>
     </row>
     <row r="36">
@@ -1536,28 +1536,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21791.42516982043</v>
+        <v>23030.17042997153</v>
       </c>
       <c r="C36" t="n">
-        <v>-1552118.054413912</v>
+        <v>-1501852.251113015</v>
       </c>
       <c r="D36" t="n">
-        <v>2042.88194839868</v>
+        <v>1782.996493651568</v>
       </c>
       <c r="E36" t="n">
-        <v>2172.006329291657</v>
+        <v>2345.278627385857</v>
       </c>
       <c r="F36" t="n">
-        <v>1859.915474411945</v>
+        <v>1834.494843873508</v>
       </c>
       <c r="G36" t="n">
-        <v>2104.110157387791</v>
+        <v>2081.486966879251</v>
       </c>
       <c r="H36" t="n">
-        <v>103.1258581069921</v>
+        <v>109.3186371508205</v>
       </c>
       <c r="I36" t="n">
-        <v>165.0615641536402</v>
+        <v>108.0189398466268</v>
       </c>
     </row>
     <row r="37">
@@ -1567,28 +1567,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-43827.74649963668</v>
+        <v>81561.58690815931</v>
       </c>
       <c r="C37" t="n">
-        <v>-1626757.537959811</v>
+        <v>-1655194.634405044</v>
       </c>
       <c r="D37" t="n">
-        <v>2198.842726500836</v>
+        <v>1950.329541960096</v>
       </c>
       <c r="E37" t="n">
-        <v>2111.04263829281</v>
+        <v>2379.324987288261</v>
       </c>
       <c r="F37" t="n">
-        <v>1774.271338354229</v>
+        <v>1920.762630422564</v>
       </c>
       <c r="G37" t="n">
-        <v>2103.881860868154</v>
+        <v>2089.219946824091</v>
       </c>
       <c r="H37" t="n">
-        <v>98.12903820727773</v>
+        <v>125.358201698614</v>
       </c>
       <c r="I37" t="n">
-        <v>116.6001064044429</v>
+        <v>106.7298782845845</v>
       </c>
     </row>
     <row r="38">
@@ -1598,28 +1598,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-44681.35335899191</v>
+        <v>-11811.57677498413</v>
       </c>
       <c r="C38" t="n">
-        <v>-1763164.288159254</v>
+        <v>-1710031.206883909</v>
       </c>
       <c r="D38" t="n">
-        <v>2335.840100227469</v>
+        <v>1771.950017453361</v>
       </c>
       <c r="E38" t="n">
-        <v>2155.528081385331</v>
+        <v>2623.539168989619</v>
       </c>
       <c r="F38" t="n">
-        <v>1777.562315303276</v>
+        <v>1795.841380821644</v>
       </c>
       <c r="G38" t="n">
-        <v>2103.100283214343</v>
+        <v>2081.737380308723</v>
       </c>
       <c r="H38" t="n">
-        <v>119.7972890277202</v>
+        <v>105.6730812359123</v>
       </c>
       <c r="I38" t="n">
-        <v>116.8090513886571</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="39">
@@ -1629,28 +1629,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4890.257516192272</v>
+        <v>-24302.49786706036</v>
       </c>
       <c r="C39" t="n">
-        <v>-1547368.695344641</v>
+        <v>-1590201.818867202</v>
       </c>
       <c r="D39" t="n">
-        <v>2048.651574572527</v>
+        <v>1835.342479358777</v>
       </c>
       <c r="E39" t="n">
-        <v>2158.785569046792</v>
+        <v>2400.80473396067</v>
       </c>
       <c r="F39" t="n">
-        <v>1838.348908883978</v>
+        <v>1771.895466931472</v>
       </c>
       <c r="G39" t="n">
-        <v>2103.001390168731</v>
+        <v>2099.32302553316</v>
       </c>
       <c r="H39" t="n">
-        <v>99.25944544277972</v>
+        <v>105.6740502399643</v>
       </c>
       <c r="I39" t="n">
-        <v>110.3226731484455</v>
+        <v>130.7057815784713</v>
       </c>
     </row>
     <row r="40">
@@ -1660,28 +1660,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3976.376312001143</v>
+        <v>-29522.89826670941</v>
       </c>
       <c r="C40" t="n">
-        <v>-1853138.462931137</v>
+        <v>-1643645.49880469</v>
       </c>
       <c r="D40" t="n">
-        <v>2511.122582391522</v>
+        <v>1904.871204746039</v>
       </c>
       <c r="E40" t="n">
-        <v>2103.505427169775</v>
+        <v>2401.496762677542</v>
       </c>
       <c r="F40" t="n">
-        <v>1846.872365288932</v>
+        <v>1770.23235528616</v>
       </c>
       <c r="G40" t="n">
-        <v>2103.011484563582</v>
+        <v>2084.543187067284</v>
       </c>
       <c r="H40" t="n">
-        <v>99.28933285694245</v>
+        <v>115.579649213155</v>
       </c>
       <c r="I40" t="n">
-        <v>139.4963300483141</v>
+        <v>108.9247482098536</v>
       </c>
     </row>
     <row r="41">
@@ -1691,28 +1691,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11311.90448651183</v>
+        <v>62225.76682351949</v>
       </c>
       <c r="C41" t="n">
-        <v>-1465435.006637142</v>
+        <v>-1490081.447028588</v>
       </c>
       <c r="D41" t="n">
-        <v>1994.009090778415</v>
+        <v>1771.080184975532</v>
       </c>
       <c r="E41" t="n">
-        <v>2108.959633285923</v>
+        <v>2345.658599187506</v>
       </c>
       <c r="F41" t="n">
-        <v>1841.524903011086</v>
+        <v>1883.019279524648</v>
       </c>
       <c r="G41" t="n">
-        <v>2105.702931167632</v>
+        <v>2085.77478558656</v>
       </c>
       <c r="H41" t="n">
-        <v>108.408620541976</v>
+        <v>115.9287316171989</v>
       </c>
       <c r="I41" t="n">
-        <v>109.9724551394618</v>
+        <v>221.8292160244583</v>
       </c>
     </row>
     <row r="42">
@@ -1722,28 +1722,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-44107.81375559652</v>
+        <v>-28616.56470522797</v>
       </c>
       <c r="C42" t="n">
-        <v>-1568329.858832032</v>
+        <v>-1613032.235561889</v>
       </c>
       <c r="D42" t="n">
-        <v>2070.629167878595</v>
+        <v>1931.077479207731</v>
       </c>
       <c r="E42" t="n">
-        <v>2161.529046441271</v>
+        <v>2334.517651242796</v>
       </c>
       <c r="F42" t="n">
-        <v>1770.011161532615</v>
+        <v>1770.80508427141</v>
       </c>
       <c r="G42" t="n">
-        <v>2109.089279291009</v>
+        <v>2081.019786209644</v>
       </c>
       <c r="H42" t="n">
-        <v>132.667682355089</v>
+        <v>105.6247779986361</v>
       </c>
       <c r="I42" t="n">
-        <v>114.0801347832572</v>
+        <v>129.6071140366706</v>
       </c>
     </row>
     <row r="43">
@@ -1753,28 +1753,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>35884.42668590788</v>
+        <v>-31702.26504039532</v>
       </c>
       <c r="C43" t="n">
-        <v>-1351363.421748564</v>
+        <v>-1764253.688002939</v>
       </c>
       <c r="D43" t="n">
-        <v>1814.445273131918</v>
+        <v>2376.890463090037</v>
       </c>
       <c r="E43" t="n">
-        <v>2164.775951123573</v>
+        <v>2090.155881263941</v>
       </c>
       <c r="F43" t="n">
-        <v>1860.070133221175</v>
+        <v>1770.005245614808</v>
       </c>
       <c r="G43" t="n">
-        <v>2103.029447061916</v>
+        <v>2081.152300574925</v>
       </c>
       <c r="H43" t="n">
-        <v>102.5468387633512</v>
+        <v>124.077605852601</v>
       </c>
       <c r="I43" t="n">
-        <v>106.2380070423562</v>
+        <v>164.1775209024902</v>
       </c>
     </row>
     <row r="44">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13657.14189267578</v>
+        <v>26125.72166400263</v>
       </c>
       <c r="C44" t="n">
-        <v>-1745578.349181063</v>
+        <v>-1622486.385273483</v>
       </c>
       <c r="D44" t="n">
-        <v>2364.416877234198</v>
+        <v>2115.063648087362</v>
       </c>
       <c r="E44" t="n">
-        <v>2107.720254866264</v>
+        <v>2167.166862367499</v>
       </c>
       <c r="F44" t="n">
-        <v>1856.868931567764</v>
+        <v>1845.865885478821</v>
       </c>
       <c r="G44" t="n">
-        <v>2104.216204648587</v>
+        <v>2081.045242047006</v>
       </c>
       <c r="H44" t="n">
-        <v>105.4398113764375</v>
+        <v>111.0446951795611</v>
       </c>
       <c r="I44" t="n">
-        <v>100.4739088621126</v>
+        <v>104.3967196562919</v>
       </c>
     </row>
     <row r="45">
@@ -1815,28 +1815,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24400.56160943769</v>
+        <v>22030.39345450047</v>
       </c>
       <c r="C45" t="n">
-        <v>-1319930.02827206</v>
+        <v>-1513506.873102417</v>
       </c>
       <c r="D45" t="n">
-        <v>1786.310032142636</v>
+        <v>1772.681200728404</v>
       </c>
       <c r="E45" t="n">
-        <v>2159.36068244122</v>
+        <v>2367.091153154323</v>
       </c>
       <c r="F45" t="n">
-        <v>1838.899250913776</v>
+        <v>1834.680261723166</v>
       </c>
       <c r="G45" t="n">
-        <v>2104.246625273438</v>
+        <v>2081.04338008953</v>
       </c>
       <c r="H45" t="n">
-        <v>103.8436231756213</v>
+        <v>135.3097312122488</v>
       </c>
       <c r="I45" t="n">
-        <v>108.3528990460005</v>
+        <v>111.9862158668444</v>
       </c>
     </row>
     <row r="46">
@@ -1846,28 +1846,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-19644.43166830437</v>
+        <v>40339.76081722323</v>
       </c>
       <c r="C46" t="n">
-        <v>-1331369.176448724</v>
+        <v>-1381923.476842367</v>
       </c>
       <c r="D46" t="n">
-        <v>1813.754094923061</v>
+        <v>1860.075737480009</v>
       </c>
       <c r="E46" t="n">
-        <v>2141.090713121517</v>
+        <v>2134.692117618366</v>
       </c>
       <c r="F46" t="n">
-        <v>1780.961515842867</v>
+        <v>1841.977781025619</v>
       </c>
       <c r="G46" t="n">
-        <v>2103.01631814021</v>
+        <v>2081.377173777208</v>
       </c>
       <c r="H46" t="n">
-        <v>103.518110238729</v>
+        <v>112.1782516704023</v>
       </c>
       <c r="I46" t="n">
-        <v>103.5792358427754</v>
+        <v>123.2194540866352</v>
       </c>
     </row>
     <row r="47">
@@ -1877,28 +1877,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40454.49796314118</v>
+        <v>-36019.457058731</v>
       </c>
       <c r="C47" t="n">
-        <v>-1313381.284423963</v>
+        <v>-1857230.892202823</v>
       </c>
       <c r="D47" t="n">
-        <v>1785.876596809</v>
+        <v>1945.798486735761</v>
       </c>
       <c r="E47" t="n">
-        <v>2154.651007461706</v>
+        <v>2644.114776027866</v>
       </c>
       <c r="F47" t="n">
-        <v>1859.158735784553</v>
+        <v>1770.513994242886</v>
       </c>
       <c r="G47" t="n">
-        <v>2104.209957183623</v>
+        <v>2081.061596821944</v>
       </c>
       <c r="H47" t="n">
-        <v>99.50267473914124</v>
+        <v>102.7264316888148</v>
       </c>
       <c r="I47" t="n">
-        <v>124.5856676792162</v>
+        <v>103.5580979144267</v>
       </c>
     </row>
     <row r="48">
@@ -1908,28 +1908,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-16881.77847393462</v>
+        <v>19435.31422199169</v>
       </c>
       <c r="C48" t="n">
-        <v>-1416373.392275411</v>
+        <v>-1566096.354860901</v>
       </c>
       <c r="D48" t="n">
-        <v>1907.066361890736</v>
+        <v>1861.11124714693</v>
       </c>
       <c r="E48" t="n">
-        <v>2140.571620490494</v>
+        <v>2345.278627385857</v>
       </c>
       <c r="F48" t="n">
-        <v>1794.538532572602</v>
+        <v>1834.494843873508</v>
       </c>
       <c r="G48" t="n">
-        <v>2109.86399283222</v>
+        <v>2081.010264004054</v>
       </c>
       <c r="H48" t="n">
-        <v>129.0125559980791</v>
+        <v>135.3633963845219</v>
       </c>
       <c r="I48" t="n">
-        <v>116.5223476595289</v>
+        <v>107.7598367129172</v>
       </c>
     </row>
     <row r="49">
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-37776.3069793731</v>
+        <v>-32392.46605383232</v>
       </c>
       <c r="C49" t="n">
-        <v>-1582879.954224287</v>
+        <v>-1781928.139773038</v>
       </c>
       <c r="D49" t="n">
-        <v>1838.428800000616</v>
+        <v>1840.793221090794</v>
       </c>
       <c r="E49" t="n">
-        <v>2413.060525214211</v>
+        <v>2649.382084877793</v>
       </c>
       <c r="F49" t="n">
-        <v>1781.766818346789</v>
+        <v>1770.389378517544</v>
       </c>
       <c r="G49" t="n">
-        <v>2104.353155881144</v>
+        <v>2089.257473282202</v>
       </c>
       <c r="H49" t="n">
-        <v>97.02616921677073</v>
+        <v>120.5347848276369</v>
       </c>
       <c r="I49" t="n">
-        <v>107.8791895369515</v>
+        <v>111.490827231156</v>
       </c>
     </row>
     <row r="50">
@@ -1970,28 +1970,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-48840.798697141</v>
+        <v>20991.0952064693</v>
       </c>
       <c r="C50" t="n">
-        <v>-1706241.650701354</v>
+        <v>-1257436.309541654</v>
       </c>
       <c r="D50" t="n">
-        <v>2252.060659644558</v>
+        <v>1771.950017453361</v>
       </c>
       <c r="E50" t="n">
-        <v>2163.235865883084</v>
+        <v>2086.002703495301</v>
       </c>
       <c r="F50" t="n">
-        <v>1770.37733700684</v>
+        <v>1795.841380821644</v>
       </c>
       <c r="G50" t="n">
-        <v>2103.334425840377</v>
+        <v>2081.737380308723</v>
       </c>
       <c r="H50" t="n">
-        <v>90.01016585641517</v>
+        <v>105.6730812359123</v>
       </c>
       <c r="I50" t="n">
-        <v>126.8551238317572</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="51">
@@ -2001,28 +2001,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-30963.77353705838</v>
+        <v>-13723.4186215899</v>
       </c>
       <c r="C51" t="n">
-        <v>-1665784.299290694</v>
+        <v>-1433443.300529282</v>
       </c>
       <c r="D51" t="n">
-        <v>2256.742671472341</v>
+        <v>1954.052810196627</v>
       </c>
       <c r="E51" t="n">
-        <v>2105.973961841012</v>
+        <v>2096.300317726343</v>
       </c>
       <c r="F51" t="n">
-        <v>1793.138766683686</v>
+        <v>1774.407640372573</v>
       </c>
       <c r="G51" t="n">
-        <v>2103.104447040343</v>
+        <v>2081.387212491548</v>
       </c>
       <c r="H51" t="n">
-        <v>119.7972890277202</v>
+        <v>104.9758437932245</v>
       </c>
       <c r="I51" t="n">
-        <v>102.0029931160562</v>
+        <v>121.1552999185911</v>
       </c>
     </row>
     <row r="52">
@@ -2032,28 +2032,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-29709.17078246968</v>
+        <v>-8249.464670972433</v>
       </c>
       <c r="C52" t="n">
-        <v>-1437627.780912742</v>
+        <v>-1362867.239542797</v>
       </c>
       <c r="D52" t="n">
-        <v>1967.170111948224</v>
+        <v>1773.810371973025</v>
       </c>
       <c r="E52" t="n">
-        <v>2103.000739415814</v>
+        <v>2196.087404259282</v>
       </c>
       <c r="F52" t="n">
-        <v>1781.567769519467</v>
+        <v>1770.980081684322</v>
       </c>
       <c r="G52" t="n">
-        <v>2103.000671671067</v>
+        <v>2081.036403404537</v>
       </c>
       <c r="H52" t="n">
-        <v>103.3527276910246</v>
+        <v>115.6153462329939</v>
       </c>
       <c r="I52" t="n">
-        <v>133.5695988564627</v>
+        <v>222.439293447543</v>
       </c>
     </row>
     <row r="53">
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>16421.36884546746</v>
+        <v>55186.37059105001</v>
       </c>
       <c r="C53" t="n">
-        <v>-1597494.906630072</v>
+        <v>-1575822.771408897</v>
       </c>
       <c r="D53" t="n">
-        <v>2171.60930460833</v>
+        <v>1877.333255924753</v>
       </c>
       <c r="E53" t="n">
-        <v>2103.505427169775</v>
+        <v>2344.708796671004</v>
       </c>
       <c r="F53" t="n">
-        <v>1855.204321685475</v>
+        <v>1883.019279524648</v>
       </c>
       <c r="G53" t="n">
-        <v>2104.369257355534</v>
+        <v>2085.77478558656</v>
       </c>
       <c r="H53" t="n">
-        <v>99.29287915797589</v>
+        <v>105.9939859513168</v>
       </c>
       <c r="I53" t="n">
-        <v>117.5533224941143</v>
+        <v>115.9225976221922</v>
       </c>
     </row>
     <row r="54">
@@ -2094,28 +2094,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-34166.13802565215</v>
+        <v>-29073.0003483477</v>
       </c>
       <c r="C54" t="n">
-        <v>-1604714.593924329</v>
+        <v>-1653785.762036438</v>
       </c>
       <c r="D54" t="n">
-        <v>2177.663637267789</v>
+        <v>1775.059372171863</v>
       </c>
       <c r="E54" t="n">
-        <v>2103.505427169775</v>
+        <v>2544.437033337434</v>
       </c>
       <c r="F54" t="n">
-        <v>1786.701834667267</v>
+        <v>1770.2119878177</v>
       </c>
       <c r="G54" t="n">
-        <v>2103.085552940554</v>
+        <v>2081.737380308723</v>
       </c>
       <c r="H54" t="n">
-        <v>99.29287915797589</v>
+        <v>105.1166225686438</v>
       </c>
       <c r="I54" t="n">
-        <v>121.1529005639298</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="55">
@@ -2125,28 +2125,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-18134.14834327018</v>
+        <v>-29551.99014512682</v>
       </c>
       <c r="C55" t="n">
-        <v>-1273369.748775007</v>
+        <v>-1773279.333835659</v>
       </c>
       <c r="D55" t="n">
-        <v>1773.098962812988</v>
+        <v>1840.969477761828</v>
       </c>
       <c r="E55" t="n">
-        <v>2128.726605248117</v>
+        <v>2637.50383492724</v>
       </c>
       <c r="F55" t="n">
-        <v>1770.091054186865</v>
+        <v>1772.4326188177</v>
       </c>
       <c r="G55" t="n">
-        <v>2103.01631814021</v>
+        <v>2083.142728566623</v>
       </c>
       <c r="H55" t="n">
-        <v>97.20604839254315</v>
+        <v>119.0802256818233</v>
       </c>
       <c r="I55" t="n">
-        <v>113.4291252952041</v>
+        <v>232.410090588755</v>
       </c>
     </row>
     <row r="56">
@@ -2156,28 +2156,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-12459.52463545883</v>
+        <v>52061.82105094893</v>
       </c>
       <c r="C56" t="n">
-        <v>-1285800.523448535</v>
+        <v>-1336596.569870847</v>
       </c>
       <c r="D56" t="n">
-        <v>1770.165181922655</v>
+        <v>1855.697160111827</v>
       </c>
       <c r="E56" t="n">
-        <v>2143.028979150441</v>
+        <v>2090.521575673572</v>
       </c>
       <c r="F56" t="n">
-        <v>1780.710347071941</v>
+        <v>1852.029553664951</v>
       </c>
       <c r="G56" t="n">
-        <v>2103.335162576316</v>
+        <v>2081.641157802575</v>
       </c>
       <c r="H56" t="n">
-        <v>102.3367420258623</v>
+        <v>99.92469388944636</v>
       </c>
       <c r="I56" t="n">
-        <v>108.3543741382289</v>
+        <v>107.3552316249664</v>
       </c>
     </row>
     <row r="57">
@@ -2187,28 +2187,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-40173.88859041547</v>
+        <v>-10001.78423548117</v>
       </c>
       <c r="C57" t="n">
-        <v>-1458422.427930508</v>
+        <v>-1626142.416647844</v>
       </c>
       <c r="D57" t="n">
-        <v>1916.461823440457</v>
+        <v>1931.769356329648</v>
       </c>
       <c r="E57" t="n">
-        <v>2175.390057255232</v>
+        <v>2352.59242313172</v>
       </c>
       <c r="F57" t="n">
-        <v>1771.109391688968</v>
+        <v>1796.935283134786</v>
       </c>
       <c r="G57" t="n">
-        <v>2103.064456114694</v>
+        <v>2081.571451355886</v>
       </c>
       <c r="H57" t="n">
-        <v>95.29871813441845</v>
+        <v>109.7814020658818</v>
       </c>
       <c r="I57" t="n">
-        <v>116.7064488188815</v>
+        <v>109.2145814033522</v>
       </c>
     </row>
     <row r="58">
@@ -2218,28 +2218,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-32794.62734832009</v>
+        <v>-65.49233901081607</v>
       </c>
       <c r="C58" t="n">
-        <v>-1396378.513790532</v>
+        <v>-1276718.551864896</v>
       </c>
       <c r="D58" t="n">
-        <v>1916.236108766134</v>
+        <v>1773.810371973025</v>
       </c>
       <c r="E58" t="n">
-        <v>2108.664632980717</v>
+        <v>2105.641677137793</v>
       </c>
       <c r="F58" t="n">
-        <v>1771.080251974847</v>
+        <v>1770.664826925874</v>
       </c>
       <c r="G58" t="n">
-        <v>2104.200447059387</v>
+        <v>2081.036403404537</v>
       </c>
       <c r="H58" t="n">
-        <v>127.2780441835696</v>
+        <v>115.6336492446846</v>
       </c>
       <c r="I58" t="n">
-        <v>116.5113745901776</v>
+        <v>129.6100864074378</v>
       </c>
     </row>
     <row r="59">
@@ -2249,28 +2249,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2279.181872376706</v>
+        <v>6595.326572686899</v>
       </c>
       <c r="C59" t="n">
-        <v>-1748754.628295166</v>
+        <v>-1316743.819003505</v>
       </c>
       <c r="D59" t="n">
-        <v>2347.403885114298</v>
+        <v>1771.125500838256</v>
       </c>
       <c r="E59" t="n">
-        <v>2128.131143330628</v>
+        <v>2149.37921247598</v>
       </c>
       <c r="F59" t="n">
-        <v>1841.511138493339</v>
+        <v>1786.423507996959</v>
       </c>
       <c r="G59" t="n">
-        <v>2103.906449403141</v>
+        <v>2081.082147789443</v>
       </c>
       <c r="H59" t="n">
-        <v>100.4287866540597</v>
+        <v>106.9133840720646</v>
       </c>
       <c r="I59" t="n">
-        <v>108.5678643387695</v>
+        <v>157.4145727957363</v>
       </c>
     </row>
     <row r="60">
@@ -2280,28 +2280,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9166.397445406765</v>
+        <v>-17893.30720211333</v>
       </c>
       <c r="C60" t="n">
-        <v>-1647315.795921916</v>
+        <v>-1541531.879060281</v>
       </c>
       <c r="D60" t="n">
-        <v>2188.367836082851</v>
+        <v>1774.276845675894</v>
       </c>
       <c r="E60" t="n">
-        <v>2152.548764401526</v>
+        <v>2397.065756052754</v>
       </c>
       <c r="F60" t="n">
-        <v>1846.033531489691</v>
+        <v>1782.029214098057</v>
       </c>
       <c r="G60" t="n">
-        <v>2105.85481586679</v>
+        <v>2087.990066412494</v>
       </c>
       <c r="H60" t="n">
-        <v>108.4935540177994</v>
+        <v>102.5623705906501</v>
       </c>
       <c r="I60" t="n">
-        <v>140.3843207048751</v>
+        <v>111.233185189754</v>
       </c>
     </row>
     <row r="61">
@@ -2311,28 +2311,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>48787.7910470264</v>
+        <v>29964.74426035164</v>
       </c>
       <c r="C61" t="n">
-        <v>-1287057.988269967</v>
+        <v>-1428909.630263717</v>
       </c>
       <c r="D61" t="n">
-        <v>1775.648345402888</v>
+        <v>1966.241067129544</v>
       </c>
       <c r="E61" t="n">
-        <v>2141.398825504447</v>
+        <v>2081.447166122469</v>
       </c>
       <c r="F61" t="n">
-        <v>1859.942643271581</v>
+        <v>1832.366442193114</v>
       </c>
       <c r="G61" t="n">
-        <v>2103.093977952053</v>
+        <v>2081.374227232061</v>
       </c>
       <c r="H61" t="n">
-        <v>97.85760465942202</v>
+        <v>132.3370960020177</v>
       </c>
       <c r="I61" t="n">
-        <v>326.7424938551703</v>
+        <v>144.2302677526086</v>
       </c>
     </row>
     <row r="62">
@@ -2342,28 +2342,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-51080.46595526161</v>
+        <v>-23071.77145038033</v>
       </c>
       <c r="C62" t="n">
-        <v>-1850748.369602695</v>
+        <v>-1511727.117329767</v>
       </c>
       <c r="D62" t="n">
-        <v>2431.421100382549</v>
+        <v>2016.159967628038</v>
       </c>
       <c r="E62" t="n">
-        <v>2176.412848802511</v>
+        <v>2126.174766987498</v>
       </c>
       <c r="F62" t="n">
-        <v>1771.48979204685</v>
+        <v>1770.016509606354</v>
       </c>
       <c r="G62" t="n">
-        <v>2109.16288108328</v>
+        <v>2081.207227974789</v>
       </c>
       <c r="H62" t="n">
-        <v>95.29970969248271</v>
+        <v>104.5712464633992</v>
       </c>
       <c r="I62" t="n">
-        <v>103.1270397542916</v>
+        <v>107.658651438933</v>
       </c>
     </row>
     <row r="63">
@@ -2373,28 +2373,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>18843.1363675301</v>
+        <v>-35105.1740980926</v>
       </c>
       <c r="C63" t="n">
-        <v>-1377058.40984784</v>
+        <v>-1853828.100591776</v>
       </c>
       <c r="D63" t="n">
-        <v>1828.083197747068</v>
+        <v>2498.473242826571</v>
       </c>
       <c r="E63" t="n">
-        <v>2178.136293361045</v>
+        <v>2087.713369271138</v>
       </c>
       <c r="F63" t="n">
-        <v>1839.527888288446</v>
+        <v>1770.007544677222</v>
       </c>
       <c r="G63" t="n">
-        <v>2103.189171549447</v>
+        <v>2081.189561850037</v>
       </c>
       <c r="H63" t="n">
-        <v>127.9129173333985</v>
+        <v>102.5750040285552</v>
       </c>
       <c r="I63" t="n">
-        <v>116.8186576866527</v>
+        <v>121.7932684968579</v>
       </c>
     </row>
     <row r="64">
@@ -2404,28 +2404,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2722.84041413432</v>
+        <v>25755.52274711849</v>
       </c>
       <c r="C64" t="n">
-        <v>-1661446.251953292</v>
+        <v>-1644866.788665786</v>
       </c>
       <c r="D64" t="n">
-        <v>1973.066025981699</v>
+        <v>1771.343535152715</v>
       </c>
       <c r="E64" t="n">
-        <v>2385.770443790479</v>
+        <v>2540.006013424334</v>
       </c>
       <c r="F64" t="n">
-        <v>1838.473861918513</v>
+        <v>1843.17929296968</v>
       </c>
       <c r="G64" t="n">
-        <v>2103.054177487224</v>
+        <v>2081.764216747869</v>
       </c>
       <c r="H64" t="n">
-        <v>99.91852095470838</v>
+        <v>127.5837762177625</v>
       </c>
       <c r="I64" t="n">
-        <v>165.1757265846809</v>
+        <v>236.0615273612853</v>
       </c>
     </row>
     <row r="65">
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-44362.7056528437</v>
+        <v>50461.21351919556</v>
       </c>
       <c r="C65" t="n">
-        <v>-1577905.694592462</v>
+        <v>-1351782.504301092</v>
       </c>
       <c r="D65" t="n">
-        <v>2083.365097747004</v>
+        <v>1861.378785104796</v>
       </c>
       <c r="E65" t="n">
-        <v>2161.529046441271</v>
+        <v>2101.276778996875</v>
       </c>
       <c r="F65" t="n">
-        <v>1770.011161532615</v>
+        <v>1852.029553664951</v>
       </c>
       <c r="G65" t="n">
-        <v>2109.089279291009</v>
+        <v>2081.641157802575</v>
       </c>
       <c r="H65" t="n">
-        <v>132.667682355089</v>
+        <v>100.2384681974116</v>
       </c>
       <c r="I65" t="n">
-        <v>113.4265720599863</v>
+        <v>107.4157286946781</v>
       </c>
     </row>
     <row r="66">
@@ -2466,28 +2466,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-24857.17290047277</v>
+        <v>-19922.79289325979</v>
       </c>
       <c r="C66" t="n">
-        <v>-1358762.320857449</v>
+        <v>-1736563.699800176</v>
       </c>
       <c r="D66" t="n">
-        <v>1807.782676146784</v>
+        <v>1877.714207594926</v>
       </c>
       <c r="E66" t="n">
-        <v>2175.999394656958</v>
+        <v>2552.622762202015</v>
       </c>
       <c r="F66" t="n">
-        <v>1776.790093630296</v>
+        <v>1785.694581330766</v>
       </c>
       <c r="G66" t="n">
-        <v>2104.256326836184</v>
+        <v>2081.177478675599</v>
       </c>
       <c r="H66" t="n">
-        <v>126.4543162028003</v>
+        <v>105.1166225686438</v>
       </c>
       <c r="I66" t="n">
-        <v>122.0297749411924</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="67">
@@ -2497,28 +2497,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-21377.59775438393</v>
+        <v>-33730.56455092086</v>
       </c>
       <c r="C67" t="n">
-        <v>-1367487.345568632</v>
+        <v>-1878894.821180443</v>
       </c>
       <c r="D67" t="n">
-        <v>1887.475916889833</v>
+        <v>1916.677801839271</v>
       </c>
       <c r="E67" t="n">
-        <v>2106.472661854094</v>
+        <v>2701.961189227587</v>
       </c>
       <c r="F67" t="n">
-        <v>1782.988974638403</v>
+        <v>1770.489113933356</v>
       </c>
       <c r="G67" t="n">
-        <v>2103.01631814021</v>
+        <v>2081.039988241276</v>
       </c>
       <c r="H67" t="n">
-        <v>103.1390462356376</v>
+        <v>104.9891669367382</v>
       </c>
       <c r="I67" t="n">
-        <v>136.0851460363599</v>
+        <v>268.1724055005525</v>
       </c>
     </row>
     <row r="68">
@@ -2528,28 +2528,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9053.299101917539</v>
+        <v>40040.42515357258</v>
       </c>
       <c r="C68" t="n">
-        <v>-1618372.244776071</v>
+        <v>-1395502.006309817</v>
       </c>
       <c r="D68" t="n">
-        <v>2198.842726500836</v>
+        <v>1774.75343971994</v>
       </c>
       <c r="E68" t="n">
-        <v>2103.505427169775</v>
+        <v>2233.515661416252</v>
       </c>
       <c r="F68" t="n">
-        <v>1846.102624097519</v>
+        <v>1844.254763071433</v>
       </c>
       <c r="G68" t="n">
-        <v>2103.011484563582</v>
+        <v>2081.717329423783</v>
       </c>
       <c r="H68" t="n">
-        <v>99.28933285694245</v>
+        <v>102.7524437210768</v>
       </c>
       <c r="I68" t="n">
-        <v>121.1529005639298</v>
+        <v>129.1645664007607</v>
       </c>
     </row>
     <row r="69">
@@ -2559,28 +2559,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-48205.17457114579</v>
+        <v>5355.40936347656</v>
       </c>
       <c r="C69" t="n">
-        <v>-1699039.063763499</v>
+        <v>-1305547.478905337</v>
       </c>
       <c r="D69" t="n">
-        <v>2298.114874051264</v>
+        <v>1771.925246484783</v>
       </c>
       <c r="E69" t="n">
-        <v>2107.709184288803</v>
+        <v>2136.362529790777</v>
       </c>
       <c r="F69" t="n">
-        <v>1771.186087209416</v>
+        <v>1781.036352038994</v>
       </c>
       <c r="G69" t="n">
-        <v>2103.034454189361</v>
+        <v>2081.737380308723</v>
       </c>
       <c r="H69" t="n">
-        <v>95.38614023936343</v>
+        <v>105.6530512477159</v>
       </c>
       <c r="I69" t="n">
-        <v>111.3366581910983</v>
+        <v>236.1271461161589</v>
       </c>
     </row>
     <row r="70">
@@ -2590,28 +2590,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-45378.43216809817</v>
+        <v>42601.21465329779</v>
       </c>
       <c r="C70" t="n">
-        <v>-1815363.509860633</v>
+        <v>-1324915.062012242</v>
       </c>
       <c r="D70" t="n">
-        <v>2389.646415286906</v>
+        <v>1849.871253120777</v>
       </c>
       <c r="E70" t="n">
-        <v>2171.252538282233</v>
+        <v>2083.062581404575</v>
       </c>
       <c r="F70" t="n">
-        <v>1778.955819895137</v>
+        <v>1837.133379805323</v>
       </c>
       <c r="G70" t="n">
-        <v>2104.202768520796</v>
+        <v>2081.247182019956</v>
       </c>
       <c r="H70" t="n">
-        <v>99.99960052362468</v>
+        <v>118.8789060207472</v>
       </c>
       <c r="I70" t="n">
-        <v>105.942415700307</v>
+        <v>102.2810259185751</v>
       </c>
     </row>
     <row r="71">
@@ -2621,28 +2621,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-46325.03940145159</v>
+        <v>52826.79475590261</v>
       </c>
       <c r="C71" t="n">
-        <v>-1807950.526835348</v>
+        <v>-1334716.042482415</v>
       </c>
       <c r="D71" t="n">
-        <v>2374.995170278311</v>
+        <v>1853.686623071092</v>
       </c>
       <c r="E71" t="n">
-        <v>2176.077832451429</v>
+        <v>2090.521575673572</v>
       </c>
       <c r="F71" t="n">
-        <v>1776.089939417516</v>
+        <v>1852.848444026162</v>
       </c>
       <c r="G71" t="n">
-        <v>2107.755157464164</v>
+        <v>2081.641157802575</v>
       </c>
       <c r="H71" t="n">
-        <v>105.831959845447</v>
+        <v>99.92469388944636</v>
       </c>
       <c r="I71" t="n">
-        <v>122.0155724233123</v>
+        <v>105.7689476868166</v>
       </c>
     </row>
     <row r="72">
@@ -2652,28 +2652,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-48499.98022300005</v>
+        <v>53198.63833170338</v>
       </c>
       <c r="C72" t="n">
-        <v>-1655493.143175761</v>
+        <v>-1363838.266432899</v>
       </c>
       <c r="D72" t="n">
-        <v>1838.428800000616</v>
+        <v>1855.503195186332</v>
       </c>
       <c r="E72" t="n">
-        <v>2508.832956771544</v>
+        <v>2120.307399460822</v>
       </c>
       <c r="F72" t="n">
-        <v>1770.064700538074</v>
+        <v>1856.976816310966</v>
       </c>
       <c r="G72" t="n">
-        <v>2103.050921616873</v>
+        <v>2081.000654738689</v>
       </c>
       <c r="H72" t="n">
-        <v>101.8317573414217</v>
+        <v>135.0702458463019</v>
       </c>
       <c r="I72" t="n">
-        <v>106.8680615227545</v>
+        <v>102.1160352963662</v>
       </c>
     </row>
     <row r="73">
@@ -2683,28 +2683,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26117.25951491715</v>
+        <v>38103.49668111326</v>
       </c>
       <c r="C73" t="n">
-        <v>-1440736.839487188</v>
+        <v>-1348579.671766296</v>
       </c>
       <c r="D73" t="n">
-        <v>1921.789724570372</v>
+        <v>1816.533425332093</v>
       </c>
       <c r="E73" t="n">
-        <v>2154.651007461706</v>
+        <v>2141.532067679053</v>
       </c>
       <c r="F73" t="n">
-        <v>1858.315497150567</v>
+        <v>1831.931164410224</v>
       </c>
       <c r="G73" t="n">
-        <v>2104.298529401002</v>
+        <v>2081.701154807838</v>
       </c>
       <c r="H73" t="n">
-        <v>100.1050823709026</v>
+        <v>138.5442881458528</v>
       </c>
       <c r="I73" t="n">
-        <v>138.6694288955825</v>
+        <v>188.0152850801497</v>
       </c>
     </row>
     <row r="74">
@@ -2714,28 +2714,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>10512.62441529846</v>
+        <v>-4179.183138552587</v>
       </c>
       <c r="C74" t="n">
-        <v>-1593270.702396335</v>
+        <v>-1345187.36161278</v>
       </c>
       <c r="D74" t="n">
-        <v>2116.478841584627</v>
+        <v>1864.332624748921</v>
       </c>
       <c r="E74" t="n">
-        <v>2152.548764401526</v>
+        <v>2088.038558021974</v>
       </c>
       <c r="F74" t="n">
-        <v>1846.033531489691</v>
+        <v>1775.179630990909</v>
       </c>
       <c r="G74" t="n">
-        <v>2105.689977512262</v>
+        <v>2081.345705830862</v>
       </c>
       <c r="H74" t="n">
-        <v>108.4935540177994</v>
+        <v>126.2449266019543</v>
       </c>
       <c r="I74" t="n">
-        <v>140.3843207048751</v>
+        <v>127.8667500998863</v>
       </c>
     </row>
     <row r="75">
@@ -2745,28 +2745,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-17622.38646664238</v>
+        <v>-244.9364848034456</v>
       </c>
       <c r="C75" t="n">
-        <v>-1893006.76754306</v>
+        <v>-1550862.110717073</v>
       </c>
       <c r="D75" t="n">
-        <v>2489.424647113344</v>
+        <v>1791.926509863962</v>
       </c>
       <c r="E75" t="n">
-        <v>2176.453051120247</v>
+        <v>2397.021814431413</v>
       </c>
       <c r="F75" t="n">
-        <v>1812.689493349097</v>
+        <v>1781.906383159408</v>
       </c>
       <c r="G75" t="n">
-        <v>2104.322523388445</v>
+        <v>2187.310585727655</v>
       </c>
       <c r="H75" t="n">
-        <v>94.1864594166188</v>
+        <v>105.6468240719227</v>
       </c>
       <c r="I75" t="n">
-        <v>393.0278893015445</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="76">
@@ -2776,28 +2776,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-9505.983569441363</v>
+        <v>83469.93223915575</v>
       </c>
       <c r="C76" t="n">
-        <v>-1382447.872176951</v>
+        <v>-1492758.485390187</v>
       </c>
       <c r="D76" t="n">
-        <v>1866.920309998235</v>
+        <v>1775.893611083792</v>
       </c>
       <c r="E76" t="n">
-        <v>2143.635139895442</v>
+        <v>2345.278627385857</v>
       </c>
       <c r="F76" t="n">
-        <v>1797.243095040323</v>
+        <v>1914.618860179588</v>
       </c>
       <c r="G76" t="n">
-        <v>2103.107104883712</v>
+        <v>2081.75436549542</v>
       </c>
       <c r="H76" t="n">
-        <v>99.56656634345146</v>
+        <v>125.3983522241774</v>
       </c>
       <c r="I76" t="n">
-        <v>315.8414659098096</v>
+        <v>153.266372891805</v>
       </c>
     </row>
     <row r="77">
@@ -2807,28 +2807,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-11662.12560110865</v>
+        <v>37092.24912206363</v>
       </c>
       <c r="C77" t="n">
-        <v>-1501952.187473881</v>
+        <v>-1414190.267446811</v>
       </c>
       <c r="D77" t="n">
-        <v>2048.692578194013</v>
+        <v>1933.996384003377</v>
       </c>
       <c r="E77" t="n">
-        <v>2103.000739415814</v>
+        <v>2096.704946703088</v>
       </c>
       <c r="F77" t="n">
-        <v>1781.567769519467</v>
+        <v>1842.231866669037</v>
       </c>
       <c r="G77" t="n">
-        <v>2245.483434513407</v>
+        <v>2081.42919017568</v>
       </c>
       <c r="H77" t="n">
-        <v>97.91601807428941</v>
+        <v>111.4297399285728</v>
       </c>
       <c r="I77" t="n">
-        <v>133.5695988564627</v>
+        <v>100.6831894990177</v>
       </c>
     </row>
     <row r="78">
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-8748.545327737927</v>
+        <v>-28930.7090945472</v>
       </c>
       <c r="C78" t="n">
-        <v>-1255499.799824172</v>
+        <v>-1599357.829871322</v>
       </c>
       <c r="D78" t="n">
-        <v>1777.208605654971</v>
+        <v>2160.017705385468</v>
       </c>
       <c r="E78" t="n">
-        <v>2103.000739415814</v>
+        <v>2087.713369271138</v>
       </c>
       <c r="F78" t="n">
-        <v>1781.540821896331</v>
+        <v>1770.007544677222</v>
       </c>
       <c r="G78" t="n">
-        <v>2103.01631814021</v>
+        <v>2081.031833042841</v>
       </c>
       <c r="H78" t="n">
-        <v>97.20604839254315</v>
+        <v>102.5570459307168</v>
       </c>
       <c r="I78" t="n">
-        <v>113.3775329055733</v>
+        <v>106.7554778169272</v>
       </c>
     </row>
     <row r="79">
@@ -2869,28 +2869,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-18943.47310540918</v>
+        <v>-35045.9087695484</v>
       </c>
       <c r="C79" t="n">
-        <v>-1431636.356436521</v>
+        <v>-1866952.655481303</v>
       </c>
       <c r="D79" t="n">
-        <v>1810.88320322695</v>
+        <v>2413.93462808896</v>
       </c>
       <c r="E79" t="n">
-        <v>2252.391710597672</v>
+        <v>2189.583172341226</v>
       </c>
       <c r="F79" t="n">
-        <v>1796.924064096272</v>
+        <v>1770.662076710149</v>
       </c>
       <c r="G79" t="n">
-        <v>2103.075811373415</v>
+        <v>2081.036186484039</v>
       </c>
       <c r="H79" t="n">
-        <v>102.5468387633512</v>
+        <v>107.5347806385938</v>
       </c>
       <c r="I79" t="n">
-        <v>100.5694473239046</v>
+        <v>122.0950887105292</v>
       </c>
     </row>
     <row r="80">
@@ -2900,28 +2900,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13029.14813968679</v>
+        <v>-28256.77003858006</v>
       </c>
       <c r="C80" t="n">
-        <v>-1504069.121210648</v>
+        <v>-1753351.164379112</v>
       </c>
       <c r="D80" t="n">
-        <v>1997.857505493166</v>
+        <v>1773.816358983984</v>
       </c>
       <c r="E80" t="n">
-        <v>2152.548764401526</v>
+        <v>2677.977362534604</v>
       </c>
       <c r="F80" t="n">
-        <v>1846.376041681541</v>
+        <v>1772.338674401747</v>
       </c>
       <c r="G80" t="n">
-        <v>2105.689977512262</v>
+        <v>2081.029430094215</v>
       </c>
       <c r="H80" t="n">
-        <v>108.408620541976</v>
+        <v>119.0816001585927</v>
       </c>
       <c r="I80" t="n">
-        <v>140.3843207048751</v>
+        <v>304.1719148613461</v>
       </c>
     </row>
     <row r="81">
@@ -2931,28 +2931,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19194.03022753214</v>
+        <v>72306.17902469961</v>
       </c>
       <c r="C81" t="n">
-        <v>-1523156.084262253</v>
+        <v>-1578468.265405887</v>
       </c>
       <c r="D81" t="n">
-        <v>2075.138692757725</v>
+        <v>2146.298014402186</v>
       </c>
       <c r="E81" t="n">
-        <v>2104.1657652933</v>
+        <v>2081.109806242288</v>
       </c>
       <c r="F81" t="n">
-        <v>1838.473861918513</v>
+        <v>1906.464945204521</v>
       </c>
       <c r="G81" t="n">
-        <v>2179.050158127723</v>
+        <v>2081.011587165277</v>
       </c>
       <c r="H81" t="n">
-        <v>99.91852095470838</v>
+        <v>111.3967585154255</v>
       </c>
       <c r="I81" t="n">
-        <v>165.1757265846809</v>
+        <v>121.5814866055649</v>
       </c>
     </row>
     <row r="82">
@@ -2962,28 +2962,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>38795.5774575579</v>
+        <v>16343.04041891778</v>
       </c>
       <c r="C82" t="n">
-        <v>-1317209.78983557</v>
+        <v>-1297103.783597172</v>
       </c>
       <c r="D82" t="n">
-        <v>1786.310032142636</v>
+        <v>1778.643442384378</v>
       </c>
       <c r="E82" t="n">
-        <v>2157.586639999769</v>
+        <v>2122.018559537217</v>
       </c>
       <c r="F82" t="n">
-        <v>1858.156943164487</v>
+        <v>1795.406984357186</v>
       </c>
       <c r="G82" t="n">
-        <v>2104.247981556061</v>
+        <v>2081.341074005265</v>
       </c>
       <c r="H82" t="n">
-        <v>103.8555340711196</v>
+        <v>105.775228521003</v>
       </c>
       <c r="I82" t="n">
-        <v>103.6531750793195</v>
+        <v>199.1536786641323</v>
       </c>
     </row>
     <row r="83">
@@ -2993,28 +2993,28 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-42817.37568292441</v>
+        <v>-24362.0664580469</v>
       </c>
       <c r="C83" t="n">
-        <v>-1533588.975973651</v>
+        <v>-1561826.136911527</v>
       </c>
       <c r="D83" t="n">
-        <v>2083.044319670076</v>
+        <v>1851.092084491079</v>
       </c>
       <c r="E83" t="n">
-        <v>2103.000739415814</v>
+        <v>2347.293439519446</v>
       </c>
       <c r="F83" t="n">
-        <v>1770.262309699064</v>
+        <v>1770.299952573969</v>
       </c>
       <c r="G83" t="n">
-        <v>2108.96800616073</v>
+        <v>2098.951866143585</v>
       </c>
       <c r="H83" t="n">
-        <v>130.5047327878997</v>
+        <v>119.0802256818233</v>
       </c>
       <c r="I83" t="n">
-        <v>124.9513580527852</v>
+        <v>137.8266243916779</v>
       </c>
     </row>
     <row r="84">
@@ -3024,28 +3024,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-35155.31439014012</v>
+        <v>74174.9575048103</v>
       </c>
       <c r="C84" t="n">
-        <v>-1673381.400273525</v>
+        <v>-1280759.02789137</v>
       </c>
       <c r="D84" t="n">
-        <v>2145.690184088751</v>
+        <v>1771.758267656564</v>
       </c>
       <c r="E84" t="n">
-        <v>2226.915575890243</v>
+        <v>2115.347310015396</v>
       </c>
       <c r="F84" t="n">
-        <v>1786.564770979762</v>
+        <v>1873.858049340336</v>
       </c>
       <c r="G84" t="n">
-        <v>2108.770240375738</v>
+        <v>2081.714314436108</v>
       </c>
       <c r="H84" t="n">
-        <v>120.6458229914063</v>
+        <v>109.7814020658818</v>
       </c>
       <c r="I84" t="n">
-        <v>105.5202181802908</v>
+        <v>107.3207540718058</v>
       </c>
     </row>
     <row r="85">
@@ -3055,28 +3055,28 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-10222.52708361251</v>
+        <v>-17755.96843263088</v>
       </c>
       <c r="C85" t="n">
-        <v>-1321889.334273838</v>
+        <v>-1522087.424847739</v>
       </c>
       <c r="D85" t="n">
-        <v>1786.310032142636</v>
+        <v>1770.039813060577</v>
       </c>
       <c r="E85" t="n">
-        <v>2159.520445821202</v>
+        <v>2376.485085084903</v>
       </c>
       <c r="F85" t="n">
-        <v>1791.912153349886</v>
+        <v>1781.191541997141</v>
       </c>
       <c r="G85" t="n">
-        <v>2104.247981556061</v>
+        <v>2081.163460587681</v>
       </c>
       <c r="H85" t="n">
-        <v>103.8555340711196</v>
+        <v>103.1111465909227</v>
       </c>
       <c r="I85" t="n">
-        <v>103.6531750793195</v>
+        <v>161.370108669673</v>
       </c>
     </row>
     <row r="86">
@@ -3086,28 +3086,28 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>41581.11500681983</v>
+        <v>-2241.563999397215</v>
       </c>
       <c r="C86" t="n">
-        <v>-1306654.110925279</v>
+        <v>-1697752.230989217</v>
       </c>
       <c r="D86" t="n">
-        <v>1779.841702368188</v>
+        <v>1774.070382649828</v>
       </c>
       <c r="E86" t="n">
-        <v>2154.651007461706</v>
+        <v>2605.826081845849</v>
       </c>
       <c r="F86" t="n">
-        <v>1859.158735784553</v>
+        <v>1810.053521712877</v>
       </c>
       <c r="G86" t="n">
-        <v>2104.209957183623</v>
+        <v>2081.550863872621</v>
       </c>
       <c r="H86" t="n">
-        <v>100.5335421342042</v>
+        <v>106.1606736127214</v>
       </c>
       <c r="I86" t="n">
-        <v>124.5856676792162</v>
+        <v>132.73014190408</v>
       </c>
     </row>
     <row r="87">
@@ -3117,28 +3117,28 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-15101.96980445227</v>
+        <v>-30251.81777936919</v>
       </c>
       <c r="C87" t="n">
-        <v>-1290972.488095041</v>
+        <v>-1776442.085019492</v>
       </c>
       <c r="D87" t="n">
-        <v>1787.677612301687</v>
+        <v>1846.297422948591</v>
       </c>
       <c r="E87" t="n">
-        <v>2130.226221385426</v>
+        <v>2636.28970186771</v>
       </c>
       <c r="F87" t="n">
-        <v>1777.665497695687</v>
+        <v>1772.210920062153</v>
       </c>
       <c r="G87" t="n">
-        <v>2104.261081489547</v>
+        <v>2081.554591570587</v>
       </c>
       <c r="H87" t="n">
-        <v>98.13508838836947</v>
+        <v>119.1867523751954</v>
       </c>
       <c r="I87" t="n">
-        <v>125.1171291179029</v>
+        <v>221.1556243999321</v>
       </c>
     </row>
     <row r="88">
@@ -3148,28 +3148,28 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-46025.00437500514</v>
+        <v>-3663.266748990398</v>
       </c>
       <c r="C88" t="n">
-        <v>-1755724.114209045</v>
+        <v>-1797852.250563488</v>
       </c>
       <c r="D88" t="n">
-        <v>2285.222170066006</v>
+        <v>2425.747724385304</v>
       </c>
       <c r="E88" t="n">
-        <v>2195.86378975206</v>
+        <v>2088.038558021974</v>
       </c>
       <c r="F88" t="n">
-        <v>1771.186087209416</v>
+        <v>1810.162104687586</v>
       </c>
       <c r="G88" t="n">
-        <v>2103.034454189361</v>
+        <v>2081.34508707747</v>
       </c>
       <c r="H88" t="n">
-        <v>95.34838746587775</v>
+        <v>126.2449266019543</v>
       </c>
       <c r="I88" t="n">
-        <v>323.9182599937687</v>
+        <v>127.8485039994063</v>
       </c>
     </row>
     <row r="89">
@@ -3179,28 +3179,28 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>17673.86303107766</v>
+        <v>14318.08133219508</v>
       </c>
       <c r="C89" t="n">
-        <v>-1496231.480408619</v>
+        <v>-1699703.591569679</v>
       </c>
       <c r="D89" t="n">
-        <v>2030.238251977678</v>
+        <v>2016.850931179525</v>
       </c>
       <c r="E89" t="n">
-        <v>2109.893720029101</v>
+        <v>2367.091153154323</v>
       </c>
       <c r="F89" t="n">
-        <v>1849.650333073559</v>
+        <v>1831.978004482967</v>
       </c>
       <c r="G89" t="n">
-        <v>2104.176723986379</v>
+        <v>2081.269642528914</v>
       </c>
       <c r="H89" t="n">
-        <v>91.99393733686946</v>
+        <v>138.2333936930706</v>
       </c>
       <c r="I89" t="n">
-        <v>283.1821193401628</v>
+        <v>111.3481417254661</v>
       </c>
     </row>
     <row r="90">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-45813.79213206051</v>
+        <v>-19683.71706219949</v>
       </c>
       <c r="C90" t="n">
-        <v>-1610636.394790058</v>
+        <v>-1475154.923473017</v>
       </c>
       <c r="D90" t="n">
-        <v>2184.404933422424</v>
+        <v>1956.336487761635</v>
       </c>
       <c r="E90" t="n">
-        <v>2104.035118758738</v>
+        <v>2142.808579858081</v>
       </c>
       <c r="F90" t="n">
-        <v>1770.007711546925</v>
+        <v>1770.734618679671</v>
       </c>
       <c r="G90" t="n">
-        <v>2107.74304170355</v>
+        <v>2081.051293823447</v>
       </c>
       <c r="H90" t="n">
-        <v>112.8694016357125</v>
+        <v>119.1028024076633</v>
       </c>
       <c r="I90" t="n">
-        <v>106.3293541660996</v>
+        <v>105.8186516736009</v>
       </c>
     </row>
     <row r="91">
@@ -3241,28 +3241,28 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-15426.15548729384</v>
+        <v>-2900.196522977203</v>
       </c>
       <c r="C91" t="n">
-        <v>-1249613.34622815</v>
+        <v>-1719664.259811454</v>
       </c>
       <c r="D91" t="n">
-        <v>1770.001788193461</v>
+        <v>1790.318387241984</v>
       </c>
       <c r="E91" t="n">
-        <v>2103.000739415814</v>
+        <v>2618.702299076914</v>
       </c>
       <c r="F91" t="n">
-        <v>1770.50757688585</v>
+        <v>1810.053521712877</v>
       </c>
       <c r="G91" t="n">
-        <v>2109.004259474409</v>
+        <v>2081.550863872621</v>
       </c>
       <c r="H91" t="n">
-        <v>97.20604839254315</v>
+        <v>106.1606736127214</v>
       </c>
       <c r="I91" t="n">
-        <v>113.4291252952041</v>
+        <v>128.0945550624614</v>
       </c>
     </row>
     <row r="92">
@@ -3272,28 +3272,28 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>51735.18039986491</v>
+        <v>-24871.40325577417</v>
       </c>
       <c r="C92" t="n">
-        <v>-1262715.483977571</v>
+        <v>-1544922.89731196</v>
       </c>
       <c r="D92" t="n">
-        <v>1784.443426386893</v>
+        <v>1773.578842416701</v>
       </c>
       <c r="E92" t="n">
-        <v>2108.690654570204</v>
+        <v>2401.496762677542</v>
       </c>
       <c r="F92" t="n">
-        <v>1859.158735784553</v>
+        <v>1770.417392493685</v>
       </c>
       <c r="G92" t="n">
-        <v>2103.096054727772</v>
+        <v>2084.543187067284</v>
       </c>
       <c r="H92" t="n">
-        <v>100.0569233660872</v>
+        <v>115.6153462329939</v>
       </c>
       <c r="I92" t="n">
-        <v>332.0146756165974</v>
+        <v>222.439293447543</v>
       </c>
     </row>
     <row r="93">
@@ -3303,28 +3303,28 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-37342.69906186359</v>
+        <v>-32341.66082268441</v>
       </c>
       <c r="C93" t="n">
-        <v>-1684771.609062853</v>
+        <v>-1729283.287214907</v>
       </c>
       <c r="D93" t="n">
-        <v>2280.438017207945</v>
+        <v>1775.62517652969</v>
       </c>
       <c r="E93" t="n">
-        <v>2107.134885558175</v>
+        <v>2644.114776027866</v>
       </c>
       <c r="F93" t="n">
-        <v>1785.390308313242</v>
+        <v>1770.513994242886</v>
       </c>
       <c r="G93" t="n">
-        <v>2103.074353625859</v>
+        <v>2081.021833538208</v>
       </c>
       <c r="H93" t="n">
-        <v>97.39640425793571</v>
+        <v>106.6166500644408</v>
       </c>
       <c r="I93" t="n">
-        <v>113.3335298178321</v>
+        <v>124.0706791471806</v>
       </c>
     </row>
     <row r="94">
@@ -3334,28 +3334,28 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-53075.39738857141</v>
+        <v>-26350.51808779268</v>
       </c>
       <c r="C94" t="n">
-        <v>-1896896.805532557</v>
+        <v>-1706347.532128174</v>
       </c>
       <c r="D94" t="n">
-        <v>2492.614254017017</v>
+        <v>2022.812791292002</v>
       </c>
       <c r="E94" t="n">
-        <v>2176.331397730668</v>
+        <v>2367.194855496398</v>
       </c>
       <c r="F94" t="n">
-        <v>1771.48979204685</v>
+        <v>1776.94699881177</v>
       </c>
       <c r="G94" t="n">
-        <v>2104.081645011268</v>
+        <v>2081.75436549542</v>
       </c>
       <c r="H94" t="n">
-        <v>95.29970969248271</v>
+        <v>125.3033507068161</v>
       </c>
       <c r="I94" t="n">
-        <v>103.9718185092763</v>
+        <v>112.900108596652</v>
       </c>
     </row>
     <row r="95">
@@ -3365,28 +3365,28 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2609.273006207775</v>
+        <v>15695.66869492317</v>
       </c>
       <c r="C95" t="n">
-        <v>-1678725.71552763</v>
+        <v>-1758590.510794929</v>
       </c>
       <c r="D95" t="n">
-        <v>2259.573171358806</v>
+        <v>1839.781111228268</v>
       </c>
       <c r="E95" t="n">
-        <v>2122.675984809659</v>
+        <v>2622.366418145422</v>
       </c>
       <c r="F95" t="n">
-        <v>1839.194978941885</v>
+        <v>1837.133379805323</v>
       </c>
       <c r="G95" t="n">
-        <v>2103.195250072603</v>
+        <v>2081.247182019956</v>
       </c>
       <c r="H95" t="n">
-        <v>99.23821274229779</v>
+        <v>118.8789060207472</v>
       </c>
       <c r="I95" t="n">
-        <v>130.0707918354765</v>
+        <v>102.2810259185751</v>
       </c>
     </row>
     <row r="96">
@@ -3396,28 +3396,28 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-22938.47548517911</v>
+        <v>45580.4879956753</v>
       </c>
       <c r="C96" t="n">
-        <v>-1348005.782468211</v>
+        <v>-1363047.956067716</v>
       </c>
       <c r="D96" t="n">
-        <v>1800.34059186445</v>
+        <v>1817.755620622991</v>
       </c>
       <c r="E96" t="n">
-        <v>2171.858524277163</v>
+        <v>2157.007741624896</v>
       </c>
       <c r="F96" t="n">
-        <v>1778.949606532717</v>
+        <v>1842.285276827756</v>
       </c>
       <c r="G96" t="n">
-        <v>2104.110012478925</v>
+        <v>2096.730238154917</v>
       </c>
       <c r="H96" t="n">
-        <v>100.0227053489637</v>
+        <v>103.1747605336714</v>
       </c>
       <c r="I96" t="n">
-        <v>105.942415700307</v>
+        <v>169.3477155830421</v>
       </c>
     </row>
     <row r="97">
@@ -3427,28 +3427,28 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26200.55782064097</v>
+        <v>6892.905458499212</v>
       </c>
       <c r="C97" t="n">
-        <v>-1518846.313356546</v>
+        <v>-1480303.31982771</v>
       </c>
       <c r="D97" t="n">
-        <v>1938.31327251169</v>
+        <v>1944.884950183708</v>
       </c>
       <c r="E97" t="n">
-        <v>2232.74710706625</v>
+        <v>2161.934958451512</v>
       </c>
       <c r="F97" t="n">
-        <v>1862.414727528778</v>
+        <v>1808.019830803187</v>
       </c>
       <c r="G97" t="n">
-        <v>2111.480556107721</v>
+        <v>2081.362951995113</v>
       </c>
       <c r="H97" t="n">
-        <v>137.7626009153171</v>
+        <v>104.8903936373791</v>
       </c>
       <c r="I97" t="n">
-        <v>164.075760963787</v>
+        <v>101.7685699411255</v>
       </c>
     </row>
     <row r="98">
@@ -3458,28 +3458,28 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-39127.52791752154</v>
+        <v>18613.19552005501</v>
       </c>
       <c r="C98" t="n">
-        <v>-1653437.287648268</v>
+        <v>-1614836.073611369</v>
       </c>
       <c r="D98" t="n">
-        <v>2241.88916358599</v>
+        <v>1861.067747000802</v>
       </c>
       <c r="E98" t="n">
-        <v>2103.566627810499</v>
+        <v>2410.061192303534</v>
       </c>
       <c r="F98" t="n">
-        <v>1776.26893786161</v>
+        <v>1834.494843873508</v>
       </c>
       <c r="G98" t="n">
-        <v>2103.37934741238</v>
+        <v>2081.203947394739</v>
       </c>
       <c r="H98" t="n">
-        <v>130.7772714531291</v>
+        <v>109.796110954723</v>
       </c>
       <c r="I98" t="n">
-        <v>308.5747092210732</v>
+        <v>161.3483988650569</v>
       </c>
     </row>
     <row r="99">
@@ -3489,28 +3489,28 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-41593.14611106226</v>
+        <v>-33064.76624729997</v>
       </c>
       <c r="C99" t="n">
-        <v>-1557947.36625358</v>
+        <v>-1739900.22196714</v>
       </c>
       <c r="D99" t="n">
-        <v>2114.867087542426</v>
+        <v>1777.518131927142</v>
       </c>
       <c r="E99" t="n">
-        <v>2103.279847263647</v>
+        <v>2656.327355468585</v>
       </c>
       <c r="F99" t="n">
-        <v>1770.506939251919</v>
+        <v>1770.383694599967</v>
       </c>
       <c r="G99" t="n">
-        <v>2103.107681748633</v>
+        <v>2081.203451100079</v>
       </c>
       <c r="H99" t="n">
-        <v>104.6391087581117</v>
+        <v>102.5123125935481</v>
       </c>
       <c r="I99" t="n">
-        <v>300.2208434932472</v>
+        <v>107.4074341069454</v>
       </c>
     </row>
     <row r="100">
@@ -3520,28 +3520,28 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-31024.5351032163</v>
+        <v>-32681.93184568081</v>
       </c>
       <c r="C100" t="n">
-        <v>-1391492.777783703</v>
+        <v>-1725539.166970125</v>
       </c>
       <c r="D100" t="n">
-        <v>1907.066361890736</v>
+        <v>1770.644687990069</v>
       </c>
       <c r="E100" t="n">
-        <v>2112.590326475329</v>
+        <v>2644.114776027866</v>
       </c>
       <c r="F100" t="n">
-        <v>1773.666343966567</v>
+        <v>1770.513994242886</v>
       </c>
       <c r="G100" t="n">
-        <v>2103.903664391577</v>
+        <v>2081.00690658464</v>
       </c>
       <c r="H100" t="n">
-        <v>96.07709973348652</v>
+        <v>102.7264316888148</v>
       </c>
       <c r="I100" t="n">
-        <v>116.5223476595289</v>
+        <v>103.5580979144267</v>
       </c>
     </row>
     <row r="101">
@@ -3551,29 +3551,46 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-17678.87544408161</v>
+        <v>56287.67809124943</v>
       </c>
       <c r="C101" t="n">
-        <v>-1742034.830426901</v>
+        <v>-1287632.256077667</v>
       </c>
       <c r="D101" t="n">
-        <v>2356.657486520615</v>
+        <v>1771.84708319541</v>
       </c>
       <c r="E101" t="n">
-        <v>2108.70188043105</v>
+        <v>2121.110689917012</v>
       </c>
       <c r="F101" t="n">
-        <v>1813.331324719175</v>
+        <v>1850.731249185496</v>
       </c>
       <c r="G101" t="n">
-        <v>2107.056101447398</v>
+        <v>2081.716657543146</v>
       </c>
       <c r="H101" t="n">
-        <v>100.750998468125</v>
+        <v>106.029383905662</v>
       </c>
       <c r="I101" t="n">
-        <v>108.0135346705244</v>
-      </c>
+        <v>107.7764238049614</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>并网选择方案</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
